--- a/hotel_booking_forms/017_urban_hotel_suite_reservation_form--hotel_booking_forms.xlsx
+++ b/hotel_booking_forms/017_urban_hotel_suite_reservation_form--hotel_booking_forms.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -427,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Guest Information Form</t>
+          <t>Guest Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -528,12 +538,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>preferences_form</t>
+          <t>room_services_form</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -541,17 +551,21 @@
           <t>Room And Services</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select the type of room and services you require.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -564,10 +578,14 @@
           <t>Payment Information</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select the payment method and provide details.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -579,41 +597,45 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>confirm_form</t>
+          <t>payment_details_form</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Confirm Booking</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Payment Details</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter the payment details below.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>confirm_booking_form</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>Confirm Booking</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -625,15 +647,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>additional_info_form</t>
+          <t>contact_us_form</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Additional Information</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>We'd love to know about any special requests or questions you have.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -648,18 +674,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>confirm_phone</t>
+          <t>phone_number_form</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Confirm Phone Number</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Phone Number</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please enter your phone number.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -671,18 +701,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>confirm_email</t>
+          <t>email_form</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Confirm Email</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please enter your email address.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -694,7 +728,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>confirm_date</t>
+          <t>date_form</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -702,10 +736,14 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please select the date of your stay.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -717,7 +755,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>confirm_time</t>
+          <t>time_form</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -725,10 +763,14 @@
           <t>Time</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please select the time of your stay.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -740,7 +782,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>confirm_note</t>
+          <t>note_form</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -748,7 +790,11 @@
           <t>Note</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Any special requests or notes?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -763,18 +809,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>confirm_phone</t>
+          <t>confirm_phone_form</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phone Number</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Confirm Phone Number</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Confirm the phone number.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -786,18 +836,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>confirm_email</t>
+          <t>confirm_email_form</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Confirm Email</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Confirm the email address.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -809,18 +863,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>confirm_date</t>
+          <t>confirm_date_form</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Confirm Date</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Confirm the date.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -832,18 +890,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>confirm_time</t>
+          <t>confirm_time_form</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Confirm Time</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Confirm the time.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -855,15 +917,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>confirm_note</t>
+          <t>confirm_note_form</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Confirm Note</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Confirm any special requests or notes.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -873,138 +939,162 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>confirm_phone</t>
+          <t>room_type_form</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phone Number</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Room Type</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Select the room type you require.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>confirm_email</t>
+          <t>bed_type_form</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Bed Type</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Select the bed type you require.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>confirm_date</t>
+          <t>meal_plan_form</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Meal Plan</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Select the meal plan you require.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>confirm_time</t>
+          <t>payment_method_form</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Payment Method</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Select the payment method.</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>confirm_note</t>
+          <t>card_number_form</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Card Number</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Enter the card number.</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>confirm_phone</t>
+          <t>expiration_date_form</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phone Number</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Expiration Date</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Enter the expiration date.</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1016,15 +1106,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>confirm_email</t>
+          <t>special_requests_form</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Special Requests</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Any special requests or notes?</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>no</t>
@@ -1034,44 +1128,106 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>confirm_date</t>
+          <t>confirm_payment_method_form</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Confirm Payment Method</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Confirm the payment method.</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>confirm_time</t>
+          <t>confirm_card_number_form</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Confirm Card Number</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Confirm the card number.</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>confirm_expiration_date_form</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Confirm Expiration Date</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Confirm the expiration date.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>confirm_special_requests_form</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Confirm Special Requests</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Confirm any special requests or notes.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1083,6 +1239,382 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>room_services_form_choices</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>double_room</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>room_services_form_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>single_room</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>room_services_form_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Suite</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>payment_info_form_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>credit_card</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Credit Card</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>payment_info_form_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>paypal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>payment_info_form_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>bank_transfer</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank Transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>confirm_booking_form_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>confirm_booking_form_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>room_type_form_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>double_room</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>room_type_form_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>single_room</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>room_type_form_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Suite</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>bed_type_form_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>single_bed</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Single Bed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>bed_type_form_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>double_bed</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Double Bed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>bed_type_form_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>king_bed</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>King Bed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>meal_plan_form_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>full_board</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Full Board</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>meal_plan_form_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>half_board</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Half Board</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>meal_plan_form_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>no_meals</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>No Meals</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>payment_method_form_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>credit_card</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Credit Card</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>payment_method_form_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>paypal</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>payment_method_form_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>bank_transfer</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Bank Transfer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
